--- a/Result/profitability/8045.xlsx
+++ b/Result/profitability/8045.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14375</v>
+        <v>0.1525</v>
       </c>
       <c r="N2" t="n">
-        <v>35.13375</v>
+        <v>35.98</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.15875</v>
+        <v>0.12375</v>
       </c>
       <c r="N3" t="n">
-        <v>36.34875</v>
+        <v>34.66875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="N4" t="n">
-        <v>35.34375</v>
+        <v>34.6975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0575</v>
+        <v>0.0775</v>
       </c>
       <c r="N5" t="n">
-        <v>35.46375</v>
+        <v>34.625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01375</v>
+        <v>-0.01875</v>
       </c>
       <c r="N6" t="n">
-        <v>34.9125</v>
+        <v>33.59375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,16 +1266,16 @@
         <v>-0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.065</v>
+        <v>-0.07375</v>
       </c>
       <c r="N7" t="n">
-        <v>33.9325</v>
+        <v>29.58</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -6020,6 +6020,133 @@
       </c>
       <c r="AM44" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8045</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>474</v>
+      </c>
+      <c r="D45" t="n">
+        <v>347</v>
+      </c>
+      <c r="E45" t="n">
+        <v>127</v>
+      </c>
+      <c r="F45" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="G45" t="n">
+        <v>17</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>16</v>
+      </c>
+      <c r="K45" t="n">
+        <v>13</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.17375</v>
+      </c>
+      <c r="N45" t="n">
+        <v>34.88500000000001</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.03000000000000001</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-0.007388252678241614</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-6.709999999999997</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-0.1998213222156044</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
